--- a/data/trans_bre/P16A15-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A15-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 7,86</t>
+          <t>0,27; 8,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 6,2</t>
+          <t>-4,3; 5,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 7,3</t>
+          <t>-1,69; 7,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 5,03</t>
+          <t>-4,01; 5,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 315,85</t>
+          <t>-3,1; 352,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,92; 99,94</t>
+          <t>-37,8; 85,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 151,98</t>
+          <t>-23,39; 154,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 50,61</t>
+          <t>-25,35; 53,3</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,15</t>
+          <t>-2,09; 4,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 7,31</t>
+          <t>-1,88; 7,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,64</t>
+          <t>-1,04; 7,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 5,87</t>
+          <t>-0,92; 6,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,69; 84,39</t>
+          <t>-27,88; 80,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 73,24</t>
+          <t>-13,65; 71,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 80,8</t>
+          <t>-9,49; 87,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 77,68</t>
+          <t>-8,43; 86,38</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 4,84</t>
+          <t>-3,4; 4,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 6,63</t>
+          <t>-3,24; 6,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 6,61</t>
+          <t>-3,11; 6,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 4,88</t>
+          <t>-3,52; 5,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 89,96</t>
+          <t>-34,8; 78,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 87,29</t>
+          <t>-26,79; 87,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 66,04</t>
+          <t>-22,44; 64,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 41,45</t>
+          <t>-21,24; 40,41</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 3,49</t>
+          <t>-2,44; 3,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 7,57</t>
+          <t>-1,88; 7,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 7,52</t>
+          <t>-2,11; 7,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 3,46</t>
+          <t>-6,63; 3,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,4; 106,05</t>
+          <t>-41,85; 110,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 94,48</t>
+          <t>-15,27; 100,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 87,74</t>
+          <t>-17,94; 91,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,85; 35,04</t>
+          <t>-46,21; 35,28</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 3,79</t>
+          <t>-7,2; 3,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 12,11</t>
+          <t>-2,0; 12,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 7,55</t>
+          <t>-3,99; 7,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 11,08</t>
+          <t>-0,16; 11,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-62,35; 98,24</t>
+          <t>-64,55; 80,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 119,18</t>
+          <t>-11,45; 126,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 88,88</t>
+          <t>-29,16; 96,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 84,94</t>
+          <t>-0,78; 87,42</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 10,67</t>
+          <t>1,84; 11,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 5,84</t>
+          <t>-5,49; 5,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 5,39</t>
+          <t>-4,48; 5,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 1,18</t>
+          <t>-9,33; 0,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,4; 330,29</t>
+          <t>17,21; 351,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 58,24</t>
+          <t>-33,44; 56,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,11; 87,87</t>
+          <t>-42,06; 89,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 7,36</t>
+          <t>-37,88; 4,55</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 5,21</t>
+          <t>-0,75; 5,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 3,71</t>
+          <t>-3,36; 4,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 2,88</t>
+          <t>-3,14; 3,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 53,08</t>
+          <t>2,53; 57,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 107,56</t>
+          <t>-9,73; 120,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 42,09</t>
+          <t>-26,76; 50,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 46,79</t>
+          <t>-33,29; 49,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,46; 594,02</t>
+          <t>22,3; 722,55</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 5,4</t>
+          <t>0,31; 5,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,95</t>
+          <t>0,04; 5,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 5,31</t>
+          <t>-0,61; 5,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 9,61</t>
+          <t>0,62; 9,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,1; 118,54</t>
+          <t>4,05; 123,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 107,86</t>
+          <t>-1,77; 102,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 69,13</t>
+          <t>-7,4; 72,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,6; 255,61</t>
+          <t>5,44; 238,56</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,38</t>
+          <t>0,83; 3,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,63</t>
+          <t>0,36; 3,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,14</t>
+          <t>0,16; 3,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 23,36</t>
+          <t>1,59; 22,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,64; 63,22</t>
+          <t>13,13; 61,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,49; 37,98</t>
+          <t>3,86; 38,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 35,28</t>
+          <t>1,35; 34,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>12,59; 222,99</t>
+          <t>13,57; 227,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A15-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A15-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 8,26</t>
+          <t>0,19; 8,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 5,55</t>
+          <t>-4,24; 6,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 7,4</t>
+          <t>-1,87; 7,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 5,35</t>
+          <t>-4,32; 4,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 352,96</t>
+          <t>-1,06; 330,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,8; 85,28</t>
+          <t>-37,25; 99,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,39; 154,55</t>
+          <t>-20,82; 159,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 53,3</t>
+          <t>-28,69; 47,86</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>2,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,32</t>
+          <t>-1,8; 4,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 7,24</t>
+          <t>-2,02; 7,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 7,36</t>
+          <t>-1,31; 6,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 6,36</t>
+          <t>-0,8; 5,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 80,49</t>
+          <t>-22,45; 94,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 71,54</t>
+          <t>-15,21; 72,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 87,0</t>
+          <t>-12,1; 81,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 86,38</t>
+          <t>-8,17; 77,38</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 4,56</t>
+          <t>-4,46; 4,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 6,74</t>
+          <t>-3,23; 6,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 6,51</t>
+          <t>-3,79; 6,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 5,26</t>
+          <t>-4,18; 4,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,8; 78,97</t>
+          <t>-41,99; 73,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 87,54</t>
+          <t>-24,63; 87,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 64,47</t>
+          <t>-26,62; 72,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 40,41</t>
+          <t>-24,0; 38,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-9,62%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 3,55</t>
+          <t>-2,35; 3,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 7,9</t>
+          <t>-1,96; 7,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 7,78</t>
+          <t>-2,12; 7,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 3,39</t>
+          <t>-3,09; 5,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,85; 110,43</t>
+          <t>-40,02; 119,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 100,74</t>
+          <t>-14,62; 95,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 91,11</t>
+          <t>-17,25; 86,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,21; 35,28</t>
+          <t>-21,83; 61,79</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,67</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 3,22</t>
+          <t>-6,4; 3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 12,5</t>
+          <t>-1,91; 11,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 7,86</t>
+          <t>-4,76; 7,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 11,25</t>
+          <t>0,27; 10,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-64,55; 80,3</t>
+          <t>-65,51; 90,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 126,74</t>
+          <t>-12,06; 114,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 96,9</t>
+          <t>-33,01; 82,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 87,42</t>
+          <t>1,39; 90,43</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-4,05</t>
+          <t>-3,39</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-19,34%</t>
+          <t>-16,57%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 11,05</t>
+          <t>2,17; 10,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 5,69</t>
+          <t>-5,1; 5,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 5,42</t>
+          <t>-4,84; 5,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 0,76</t>
+          <t>-9,34; 1,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,21; 351,74</t>
+          <t>24,12; 377,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 56,83</t>
+          <t>-33,48; 62,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 89,0</t>
+          <t>-43,94; 87,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,88; 4,55</t>
+          <t>-38,8; 7,09</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24,23</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>227,56%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,0</t>
+          <t>-0,95; 4,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,24</t>
+          <t>-3,64; 3,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,01</t>
+          <t>-3,31; 3,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 57,93</t>
+          <t>-0,01; 6,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 120,37</t>
+          <t>-13,14; 112,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,76; 50,01</t>
+          <t>-28,99; 42,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 49,79</t>
+          <t>-35,16; 48,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,3; 722,55</t>
+          <t>-0,8; 65,97</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 5,61</t>
+          <t>0,29; 5,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 5,9</t>
+          <t>0,2; 5,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,63</t>
+          <t>-0,85; 5,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 9,74</t>
+          <t>-0,65; 4,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,05; 123,04</t>
+          <t>2,19; 118,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 102,16</t>
+          <t>2,5; 99,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 72,64</t>
+          <t>-8,92; 70,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,44; 238,56</t>
+          <t>-5,08; 55,48</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>1,9</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,24</t>
+          <t>0,86; 3,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,68</t>
+          <t>0,44; 3,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,1</t>
+          <t>0,1; 3,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,59; 22,44</t>
+          <t>0,58; 3,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,13; 61,62</t>
+          <t>13,46; 62,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,86; 38,66</t>
+          <t>3,95; 36,93</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 34,84</t>
+          <t>0,76; 35,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,57; 227,26</t>
+          <t>4,5; 28,87</t>
         </is>
       </c>
     </row>
